--- a/utils/monday_sprint_sprint_2025-16.xlsx
+++ b/utils/monday_sprint_sprint_2025-16.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="286">
   <si>
     <t>Ticket</t>
   </si>
@@ -405,6 +405,9 @@
     <t>10/02/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Fevereiro</t>
   </si>
   <si>
@@ -648,7 +651,7 @@
     <t>25/06/2025</t>
   </si>
   <si>
-    <t>22/03/2026</t>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>32387</t>
@@ -3224,7 +3227,7 @@
         <v>129</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>31</v>
@@ -3233,7 +3236,7 @@
         <v>32</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -3250,7 +3253,7 @@
         <v>76</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>17</v>
@@ -3282,7 +3285,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3294,10 +3297,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3326,7 +3329,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3338,10 +3341,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3370,7 +3373,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3382,10 +3385,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
@@ -3414,7 +3417,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3426,10 +3429,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3447,7 +3450,7 @@
         <v>17</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>40</v>
@@ -3458,7 +3461,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3470,10 +3473,10 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
@@ -3502,7 +3505,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3514,10 +3517,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3546,7 +3549,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3558,10 +3561,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>19</v>
@@ -3590,7 +3593,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3602,10 +3605,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
@@ -3634,7 +3637,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3646,10 +3649,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>19</v>
@@ -3678,7 +3681,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3690,10 +3693,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3722,7 +3725,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3734,10 +3737,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3766,7 +3769,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3778,10 +3781,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3810,7 +3813,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3822,10 +3825,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3866,7 +3869,7 @@
         <v>76</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>17</v>
@@ -3898,7 +3901,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -3910,10 +3913,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -3942,7 +3945,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3954,25 +3957,25 @@
         <v>76</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>80</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>20</v>
@@ -3986,7 +3989,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3998,10 +4001,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -4030,7 +4033,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4042,10 +4045,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
@@ -4074,7 +4077,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4086,10 +4089,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -4130,7 +4133,7 @@
         <v>76</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>17</v>
@@ -4162,7 +4165,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4174,10 +4177,10 @@
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -4206,7 +4209,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4218,10 +4221,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>19</v>
@@ -4250,7 +4253,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4262,22 +4265,22 @@
         <v>76</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>80</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>17</v>
@@ -4294,7 +4297,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4306,10 +4309,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>19</v>
@@ -4338,7 +4341,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4350,10 +4353,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
@@ -4394,7 +4397,7 @@
         <v>76</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>17</v>
@@ -4438,7 +4441,7 @@
         <v>76</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>17</v>
@@ -4470,7 +4473,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4482,10 +4485,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
@@ -4514,7 +4517,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4526,10 +4529,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4558,7 +4561,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4570,22 +4573,22 @@
         <v>76</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>17</v>
@@ -4597,12 +4600,12 @@
         <v>32</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4614,10 +4617,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>24</v>
@@ -4646,7 +4649,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4658,10 +4661,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>24</v>
@@ -4702,7 +4705,7 @@
         <v>76</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>17</v>
@@ -4746,7 +4749,7 @@
         <v>76</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>17</v>
@@ -4790,10 +4793,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>19</v>
@@ -4822,7 +4825,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -4834,10 +4837,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>19</v>
@@ -4866,7 +4869,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -4878,25 +4881,25 @@
         <v>76</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>80</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>20</v>
@@ -4910,7 +4913,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -4922,10 +4925,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -4966,7 +4969,7 @@
         <v>76</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>17</v>
@@ -4998,7 +5001,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -5010,10 +5013,10 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
@@ -5042,7 +5045,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -5054,10 +5057,10 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
@@ -5086,7 +5089,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5098,10 +5101,10 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>19</v>
@@ -5130,7 +5133,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5142,10 +5145,10 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>19</v>
@@ -5186,10 +5189,10 @@
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>19</v>
@@ -5218,7 +5221,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5230,10 +5233,10 @@
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>19</v>
@@ -5262,7 +5265,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5274,10 +5277,10 @@
         <v>17</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>19</v>
@@ -5306,7 +5309,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5318,22 +5321,22 @@
         <v>76</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>80</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>17</v>
@@ -5345,12 +5348,12 @@
         <v>40</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
@@ -5362,10 +5365,10 @@
         <v>17</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>19</v>
@@ -5394,7 +5397,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -5406,25 +5409,25 @@
         <v>76</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>20</v>
@@ -5433,12 +5436,12 @@
         <v>21</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -5450,10 +5453,10 @@
         <v>17</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>19</v>
@@ -5526,7 +5529,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -5538,10 +5541,10 @@
         <v>17</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>19</v>
@@ -5570,7 +5573,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
@@ -5582,10 +5585,10 @@
         <v>17</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>19</v>
@@ -5626,10 +5629,10 @@
         <v>17</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>19</v>
@@ -5658,7 +5661,7 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>15</v>
@@ -5670,10 +5673,10 @@
         <v>17</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>19</v>
@@ -5702,7 +5705,7 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>15</v>
@@ -5714,10 +5717,10 @@
         <v>17</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>19</v>
@@ -5758,10 +5761,10 @@
         <v>17</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>19</v>
@@ -5790,7 +5793,7 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>15</v>
@@ -5802,10 +5805,10 @@
         <v>17</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>19</v>
@@ -5834,7 +5837,7 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>15</v>
@@ -5846,10 +5849,10 @@
         <v>17</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>19</v>
@@ -5878,7 +5881,7 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>15</v>
@@ -5890,10 +5893,10 @@
         <v>17</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>19</v>
@@ -5922,7 +5925,7 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>15</v>
@@ -5934,10 +5937,10 @@
         <v>17</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>19</v>
@@ -5966,7 +5969,7 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>15</v>
@@ -5978,10 +5981,10 @@
         <v>17</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>19</v>
@@ -6010,7 +6013,7 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>15</v>
@@ -6022,10 +6025,10 @@
         <v>17</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>19</v>
@@ -6065,23 +6068,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6089,16 +6092,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6117,7 +6120,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6138,7 +6141,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6169,12 +6172,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2">
         <v>107</v>
@@ -6198,25 +6201,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6233,13 +6236,13 @@
         <v>81</v>
       </c>
       <c r="G10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -6271,7 +6274,7 @@
         <v>20</v>
       </c>
       <c r="J11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K11">
         <v>107</v>
@@ -6286,7 +6289,7 @@
         <v>32</v>
       </c>
       <c r="Q11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -6303,7 +6306,7 @@
         <v>87</v>
       </c>
       <c r="M12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -6312,7 +6315,7 @@
         <v>83</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -6323,7 +6326,7 @@
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -6343,7 +6346,7 @@
     </row>
     <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -6371,7 +6374,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6379,7 +6382,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6387,7 +6390,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -6398,7 +6401,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6406,86 +6409,86 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>193</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6496,7 +6499,7 @@
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>77</v>
@@ -6504,16 +6507,16 @@
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6524,7 +6527,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>114</v>
@@ -6538,10 +6541,10 @@
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-16.xlsx
+++ b/utils/monday_sprint_sprint_2025-16.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="319">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>31757</t>
+    <t>9270639972</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,343 +87,364 @@
     <t>30/05/2025</t>
   </si>
   <si>
+    <t>27/07/2025</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>9279941838</t>
+  </si>
+  <si>
+    <t>Melhoria no sistema de Liberação de ensaios e Ensaios destrutivos</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>02/06/2025</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>9279984119</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>IA para programação automática de máquinas de usinagem</t>
+  </si>
+  <si>
+    <t>9572339552</t>
+  </si>
+  <si>
+    <t>Inclusão de novo setor e alteração de metas</t>
+  </si>
+  <si>
+    <t>11/07/2025</t>
+  </si>
+  <si>
+    <t>09/08/2025</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>9572598938</t>
+  </si>
+  <si>
+    <t>UNIÃO APONTAMENTO ACABAMANTO E MOLDAGEM</t>
+  </si>
+  <si>
+    <t>07/08/2025</t>
+  </si>
+  <si>
+    <t>9581037762</t>
+  </si>
+  <si>
+    <t>Copiloto Gerencial IA - Descrição das Tabelas</t>
+  </si>
+  <si>
+    <t>14/07/2025</t>
+  </si>
+  <si>
+    <t>31/07/2025</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>9673871000</t>
+  </si>
+  <si>
+    <t>Bloqueio Número Modelo CPP e Cliente - FTF, OTF e CPP</t>
+  </si>
+  <si>
+    <t>25/07/2025</t>
+  </si>
+  <si>
+    <t>10/08/2025</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>9674651750</t>
+  </si>
+  <si>
+    <t>CRIAÇÃO DE DASHBOARDS - INDICADORES INSTALAÇÃO INDUSTRIAL</t>
+  </si>
+  <si>
+    <t>9674704025</t>
+  </si>
+  <si>
+    <t>Impressão Etiqueta Volvo Mercado Nacional</t>
+  </si>
+  <si>
+    <t>03/08/2025</t>
+  </si>
+  <si>
+    <t>9674716312</t>
+  </si>
+  <si>
+    <t>Incluir Rota no WMS</t>
+  </si>
+  <si>
+    <t>9684026003</t>
+  </si>
+  <si>
+    <t>Custos de Armazenagem/MP</t>
+  </si>
+  <si>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>9374699414</t>
+  </si>
+  <si>
+    <t>criar arvore de componentes</t>
+  </si>
+  <si>
+    <t>13/06/2025</t>
+  </si>
+  <si>
+    <t>04/08/2025</t>
+  </si>
+  <si>
+    <t>9374717128</t>
+  </si>
+  <si>
+    <t>DATA DE FUSÃO X PROCEDIMENTOS PRÉ-PRODUTIVO</t>
+  </si>
+  <si>
+    <t>9683896143</t>
+  </si>
+  <si>
+    <t>ALERTA DE REVISÃO X BLOQUEIO DE MODELO</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>9684139996</t>
+  </si>
+  <si>
+    <t>Viabilidade e Proposta - Retificação de SPED Fiscal</t>
+  </si>
+  <si>
+    <t>05/08/2025</t>
+  </si>
+  <si>
+    <t>9684140168</t>
+  </si>
+  <si>
+    <t>Inclusão de romaneios manualmente no Recibo de Embarque</t>
+  </si>
+  <si>
+    <t>9374707860</t>
+  </si>
+  <si>
+    <t>PROCEDIMENTO PRÉ-PRODUTIVO SETOR 540</t>
+  </si>
+  <si>
+    <t>9683895979</t>
+  </si>
+  <si>
+    <t>MELHORIAS FLUXO 109 REVISÕES (copy)</t>
+  </si>
+  <si>
+    <t>9674771798</t>
+  </si>
+  <si>
+    <t>Dados Pgto por Invoice</t>
+  </si>
+  <si>
+    <t>9684032898</t>
+  </si>
+  <si>
+    <t>Códigos dos materiais - Definição do Escopo</t>
+  </si>
+  <si>
+    <t>29/07/2025</t>
+  </si>
+  <si>
+    <t>9674088237</t>
+  </si>
+  <si>
+    <t>APONTAMENTO ELETRONICO JATO GRANDE (DIRIGIDO)</t>
+  </si>
+  <si>
+    <t>9674046273</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Lançamento x Exportação contabilização fretes</t>
+  </si>
+  <si>
+    <t>30/07/2025</t>
+  </si>
+  <si>
+    <t>9279984262</t>
+  </si>
+  <si>
+    <t>IA para a predição e dimensionamento de estoque</t>
+  </si>
+  <si>
+    <t>9581467554</t>
+  </si>
+  <si>
+    <t>Melhoria Sistema de Custeio - Usinagem Pintura - Revisão de Calculo</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>9683896086</t>
+  </si>
+  <si>
+    <t>Planilhão via Qlik sense</t>
+  </si>
+  <si>
+    <t>9673942891</t>
+  </si>
+  <si>
+    <t>Altona || Exportação de produtos consumidos - Estoque Imobilizado</t>
+  </si>
+  <si>
+    <t>9674037279</t>
+  </si>
+  <si>
+    <t>Altona || Relatório para controle de consignados a faturar</t>
+  </si>
+  <si>
+    <t>9572445336</t>
+  </si>
+  <si>
+    <t>Computador ajustagem - Desenvolvimento</t>
+  </si>
+  <si>
+    <t>9674789142</t>
+  </si>
+  <si>
+    <t>Alteração no sistema MPO - Usinagem</t>
+  </si>
+  <si>
+    <t>9674729227</t>
+  </si>
+  <si>
+    <t>APONTAMENTO PARADAS MANUTENÇÃO CORRETIVA JATO 25T</t>
+  </si>
+  <si>
+    <t>9673919720</t>
+  </si>
+  <si>
+    <t>Sistema de corridas</t>
+  </si>
+  <si>
+    <t>9674099761</t>
+  </si>
+  <si>
+    <t>Correção dos motivos de paradas</t>
+  </si>
+  <si>
+    <t>9373076706</t>
+  </si>
+  <si>
+    <t>EXCLUSÃO DE SETORES EM VÁRIAS PEÇAS SIMULTANEAMENTE</t>
+  </si>
+  <si>
+    <t>9674743060</t>
+  </si>
+  <si>
+    <t>Sequencia de Pre Produtivo</t>
+  </si>
+  <si>
+    <t>9382250097</t>
+  </si>
+  <si>
+    <t>Criar códigos de paradas</t>
+  </si>
+  <si>
+    <t>16/06/2025</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>9471656055</t>
+  </si>
+  <si>
+    <t>ORÇAR PO 120-82/25 com ACVO – Fornecimento de Rotor com Pás Semi-Ocas (( HACKER )</t>
+  </si>
+  <si>
+    <t>27/06/2025</t>
+  </si>
+  <si>
+    <t>9674835762</t>
+  </si>
+  <si>
+    <t>Tempo Log on sistema WMS Almoxarifado</t>
+  </si>
+  <si>
+    <t>9471895088</t>
+  </si>
+  <si>
+    <t>BI para análises das auditorias de CIPA</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Integração CRM - Carga Unidade Federação</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>25418</t>
-  </si>
-  <si>
-    <t>Melhoria no sistema de Liberação de ensaios e Ensaios destrutivos</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>02/06/2025</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Junho</t>
-  </si>
-  <si>
-    <t>31700</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>IA para programação automática de máquinas de usinagem</t>
-  </si>
-  <si>
-    <t>32719</t>
-  </si>
-  <si>
-    <t>Inclusão de novo setor e alteração de metas</t>
-  </si>
-  <si>
-    <t>11/07/2025</t>
-  </si>
-  <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>32512</t>
-  </si>
-  <si>
-    <t>UNIÃO APONTAMENTO ACABAMANTO E MOLDAGEM</t>
-  </si>
-  <si>
-    <t>31699</t>
-  </si>
-  <si>
-    <t>Copiloto Gerencial IA - Descrição das Tabelas</t>
-  </si>
-  <si>
-    <t>14/07/2025</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>33095</t>
-  </si>
-  <si>
-    <t>Bloqueio Número Modelo CPP e Cliente - FTF, OTF e CPP</t>
-  </si>
-  <si>
-    <t>25/07/2025</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>32933</t>
-  </si>
-  <si>
-    <t>CRIAÇÃO DE DASHBOARDS - INDICADORES INSTALAÇÃO INDUSTRIAL</t>
-  </si>
-  <si>
-    <t>32906</t>
-  </si>
-  <si>
-    <t>Impressão Etiqueta Volvo Mercado Nacional</t>
-  </si>
-  <si>
-    <t>32894</t>
-  </si>
-  <si>
-    <t>Incluir Rota no WMS</t>
-  </si>
-  <si>
-    <t>32041</t>
-  </si>
-  <si>
-    <t>Custos de Armazenagem/MP</t>
-  </si>
-  <si>
-    <t>28/07/2025</t>
-  </si>
-  <si>
-    <t>32088</t>
-  </si>
-  <si>
-    <t>criar arvore de componentes</t>
-  </si>
-  <si>
-    <t>13/06/2025</t>
-  </si>
-  <si>
-    <t>32081</t>
-  </si>
-  <si>
-    <t>DATA DE FUSÃO X PROCEDIMENTOS PRÉ-PRODUTIVO</t>
-  </si>
-  <si>
-    <t>31609</t>
-  </si>
-  <si>
-    <t>ALERTA DE REVISÃO X BLOQUEIO DE MODELO</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>32723</t>
-  </si>
-  <si>
-    <t>Viabilidade e Proposta - Retificação de SPED Fiscal</t>
-  </si>
-  <si>
-    <t>31794</t>
-  </si>
-  <si>
-    <t>Inclusão de romaneios manualmente no Recibo de Embarque</t>
-  </si>
-  <si>
-    <t>32082</t>
-  </si>
-  <si>
-    <t>PROCEDIMENTO PRÉ-PRODUTIVO SETOR 540</t>
-  </si>
-  <si>
-    <t>31270</t>
-  </si>
-  <si>
-    <t>MELHORIAS FLUXO 109 REVISÕES (copy)</t>
-  </si>
-  <si>
-    <t>32873</t>
-  </si>
-  <si>
-    <t>Dados Pgto por Invoice</t>
-  </si>
-  <si>
-    <t>32348</t>
-  </si>
-  <si>
-    <t>Códigos dos materiais - Definição do Escopo</t>
-  </si>
-  <si>
-    <t>33047</t>
-  </si>
-  <si>
-    <t>APONTAMENTO ELETRONICO JATO GRANDE (DIRIGIDO)</t>
-  </si>
-  <si>
-    <t>33055</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Lançamento x Exportação contabilização fretes</t>
-  </si>
-  <si>
-    <t>31701</t>
-  </si>
-  <si>
-    <t>IA para a predição e dimensionamento de estoque</t>
-  </si>
-  <si>
-    <t>32353</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Melhoria Sistema de Custeio - Usinagem Pintura - Revisão de Calculo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexandre, bom dia! Para Custeio Usinagem Pintura, ao invés de utilizar apontamentos de horas, valores do setor PINTURA (centro custo 8010) devem ser rateados somente para as sequências movimentadas no setor 3081. Critério de rateio deve ser proporcional de custo FTF dos setores 3081 + 3082 + 8010. </t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
+    <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
     <t>Sistemas</t>
   </si>
   <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>31685</t>
-  </si>
-  <si>
-    <t>Planilhão via Qlik sense</t>
-  </si>
-  <si>
-    <t>33066</t>
-  </si>
-  <si>
-    <t>Altona || Exportação de produtos consumidos - Estoque Imobilizado</t>
-  </si>
-  <si>
-    <t>33060</t>
-  </si>
-  <si>
-    <t>Altona || Relatório para controle de consignados a faturar</t>
-  </si>
-  <si>
-    <t>32665</t>
-  </si>
-  <si>
-    <t>Computador ajustagem - Desenvolvimento</t>
-  </si>
-  <si>
-    <t>32860</t>
-  </si>
-  <si>
-    <t>Alteração no sistema MPO - Usinagem</t>
-  </si>
-  <si>
-    <t>32893</t>
-  </si>
-  <si>
-    <t>APONTAMENTO PARADAS MANUTENÇÃO CORRETIVA JATO 25T</t>
-  </si>
-  <si>
-    <t>33075</t>
-  </si>
-  <si>
-    <t>Sistema de corridas</t>
-  </si>
-  <si>
-    <t>33044</t>
-  </si>
-  <si>
-    <t>Correção dos motivos de paradas</t>
-  </si>
-  <si>
-    <t>32201</t>
-  </si>
-  <si>
-    <t>EXCLUSÃO DE SETORES EM VÁRIAS PEÇAS SIMULTANEAMENTE</t>
-  </si>
-  <si>
-    <t>32890</t>
-  </si>
-  <si>
-    <t>Sequencia de Pre Produtivo</t>
-  </si>
-  <si>
-    <t>31753</t>
-  </si>
-  <si>
-    <t>Criar códigos de paradas</t>
-  </si>
-  <si>
-    <t>16/06/2025</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>32519</t>
-  </si>
-  <si>
-    <t>ORÇAR PO 120-82/25 com ACVO – Fornecimento de Rotor com Pás Semi-Ocas (( HACKER )</t>
-  </si>
-  <si>
-    <t>27/06/2025</t>
-  </si>
-  <si>
-    <t>32859</t>
-  </si>
-  <si>
-    <t>Tempo Log on sistema WMS Almoxarifado</t>
-  </si>
-  <si>
-    <t>32404</t>
-  </si>
-  <si>
-    <t>BI para análises das auditorias de CIPA</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Integração CRM - Carga Unidade Federação</t>
-  </si>
-  <si>
-    <t>Laura Herrmann Schmickler</t>
-  </si>
-  <si>
     <t>16/07/2025</t>
   </si>
   <si>
-    <t>26571</t>
+    <t>9684140771</t>
   </si>
   <si>
     <t>Retirar de peças do deposito para versão WMS (copy)</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>9683940215</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -432,7 +453,7 @@
     <t>Permitir informar mais de um cliente na tela do agendamento</t>
   </si>
   <si>
-    <t>32080</t>
+    <t>9683896449</t>
   </si>
   <si>
     <t>GRUPO DE RECURSOS PADRÃO</t>
@@ -441,6 +462,9 @@
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Saneamento de dados para APS</t>
   </si>
   <si>
@@ -462,19 +486,19 @@
     <t>Apontamento Quebra de Canal - Homologação</t>
   </si>
   <si>
-    <t>32786</t>
+    <t>9684140631</t>
   </si>
   <si>
     <t>Ações reunião sobre app da USE</t>
   </si>
   <si>
-    <t>32857</t>
+    <t>9674856215</t>
   </si>
   <si>
     <t>Melhorias dentro do sistema wms pré-lista</t>
   </si>
   <si>
-    <t>32858</t>
+    <t>9674846652</t>
   </si>
   <si>
     <t>[NIMBI] API's para a integração de requisição gerado no ERP &gt; Nimbi</t>
@@ -483,31 +507,31 @@
     <t>Impedimento</t>
   </si>
   <si>
-    <t>30905</t>
+    <t>9683896398</t>
   </si>
   <si>
     <t>ACVO - REUNIÃO (copy)</t>
   </si>
   <si>
-    <t>32854</t>
+    <t>9674912329</t>
   </si>
   <si>
     <t>Indicadores SGI</t>
   </si>
   <si>
-    <t>33002</t>
+    <t>9674187921</t>
   </si>
   <si>
     <t>ERRO: Relatório ESTOQUE_DEPOSITO_FABRIL_SEQUENCIAS</t>
   </si>
   <si>
-    <t>32856</t>
+    <t>9674890672</t>
   </si>
   <si>
     <t>Termo de responsabilidade assinatura digital ( EPI's )</t>
   </si>
   <si>
-    <t>32002</t>
+    <t>9481001263</t>
   </si>
   <si>
     <t>Apontamento IROG-BI moldagem USE</t>
@@ -522,19 +546,19 @@
     <t>Inventario WMS - Registro de Ajuste de Box</t>
   </si>
   <si>
-    <t>32425</t>
+    <t>9471846228</t>
   </si>
   <si>
     <t>Precisamos que SPS conecte ao WMS</t>
   </si>
   <si>
-    <t>33008</t>
+    <t>9674165828</t>
   </si>
   <si>
     <t>APONTAMENTO IMPRODUTIVOS MANIPULADORES</t>
   </si>
   <si>
-    <t>31292</t>
+    <t>9684180671</t>
   </si>
   <si>
     <t>Apontamento eletrônico corte pó de ferro  - Homologação</t>
@@ -543,7 +567,7 @@
     <t>Integração CRM - Transportadora</t>
   </si>
   <si>
-    <t>32803</t>
+    <t>9571966329</t>
   </si>
   <si>
     <t>Inclusão de campo na tabela PREVEN</t>
@@ -561,19 +585,19 @@
     <t>Jacson Schneider Movidesk</t>
   </si>
   <si>
-    <t>32852</t>
+    <t>9571671835</t>
   </si>
   <si>
     <t>[COMPRAS] Inclusão de campos Cadastro item + Inclusão de campos Relatório de materiais</t>
   </si>
   <si>
-    <t>32957</t>
+    <t>9674573370</t>
   </si>
   <si>
     <t>EXCLUSÃO DE CLIENTE DA FTF</t>
   </si>
   <si>
-    <t>32970</t>
+    <t>9674231506</t>
   </si>
   <si>
     <t>Ajuste no Sistema de Impressão de etiquetas corpo de prova</t>
@@ -582,13 +606,13 @@
     <t>Integração CRM - Carga Ofertas</t>
   </si>
   <si>
-    <t>32050</t>
+    <t>9675393759</t>
   </si>
   <si>
     <t>Inativar Romaneio</t>
   </si>
   <si>
-    <t>32789</t>
+    <t>9683773114</t>
   </si>
   <si>
     <t>Bloco K - Envio dos dados do cálculo do custos para base de dados - Apresentação</t>
@@ -597,6 +621,9 @@
     <t>32141</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Cadastro de Embalagem no CPP</t>
   </si>
   <si>
@@ -612,13 +639,13 @@
     <t>02/06/2026</t>
   </si>
   <si>
-    <t>32160</t>
+    <t>9675346434</t>
   </si>
   <si>
     <t>Inventario WMS - Expedição</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>9684025572</t>
   </si>
   <si>
     <t>Integração de faturamentos com eventos</t>
@@ -630,13 +657,13 @@
     <t>Integração CRM - Estados</t>
   </si>
   <si>
-    <t>28583</t>
+    <t>9684307004</t>
   </si>
   <si>
     <t>Compara Carteira UPR - Erro</t>
   </si>
   <si>
-    <t>33125</t>
+    <t>9675627040</t>
   </si>
   <si>
     <t>Alteração Histórico de Faturamento</t>
@@ -651,13 +678,13 @@
     <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
   </si>
   <si>
-    <t>32310</t>
+    <t>9684180824</t>
   </si>
   <si>
     <t>Retrabalho da moldagem - Classificação</t>
   </si>
   <si>
-    <t>32298</t>
+    <t>9683984312</t>
   </si>
   <si>
     <t>Mapeamento Digital</t>
@@ -669,10 +696,13 @@
     <t>Integração CRM - Setor consumo</t>
   </si>
   <si>
+    <t>9683953542</t>
+  </si>
+  <si>
     <t>Analisar TAG's, conforme planner utilizado na expedição e adaptar no agendamento de coleta</t>
   </si>
   <si>
-    <t>32759</t>
+    <t>9684307431</t>
   </si>
   <si>
     <t>Paradas no BI</t>
@@ -696,61 +726,67 @@
     <t>17/03/2026</t>
   </si>
   <si>
-    <t>32387</t>
+    <t>9684307315</t>
   </si>
   <si>
     <t>Desenvolvimento de gráfico - aplicação Refugo Qlik Sense - Homologação (copy)</t>
   </si>
   <si>
+    <t>06/08/2025</t>
+  </si>
+  <si>
     <t>Integração CRM - Tarefa para disparar integrações</t>
   </si>
   <si>
-    <t>32945</t>
+    <t>9674639647</t>
   </si>
   <si>
     <t>Aplicativo Corte de canais Pó de ferro</t>
   </si>
   <si>
-    <t>31233</t>
+    <t>9684025653</t>
   </si>
   <si>
     <t>Integração faturamento x Benner  Reunião de entrega</t>
   </si>
   <si>
-    <t>32073</t>
+    <t>9675379822</t>
   </si>
   <si>
     <t>Diferenças planilha</t>
   </si>
   <si>
-    <t>32363</t>
+    <t>9684025807</t>
   </si>
   <si>
     <t>Planejamento de capacidade MOxdemanda de preventivas no sistema de manutenção (copy) (copy)</t>
   </si>
   <si>
+    <t>9684857243</t>
+  </si>
+  <si>
     <t>Revisar filtro de Rotulo</t>
   </si>
   <si>
-    <t>32849</t>
+    <t>9684025862</t>
   </si>
   <si>
     <t>ALTERAÇÃO VENCIMENTO VOLVO DO BRASIL</t>
   </si>
   <si>
-    <t>32875</t>
+    <t>9674752560</t>
   </si>
   <si>
     <t>Rateio Tempo Padrão</t>
   </si>
   <si>
-    <t>31836</t>
+    <t>9684025733</t>
   </si>
   <si>
     <t>Melhoria WMS - Conferencia e Carregamento</t>
   </si>
   <si>
-    <t>32287</t>
+    <t>9684307497</t>
   </si>
   <si>
     <t>Aplicação de controle de consumo e custo de PROEX e Antecipação de Caterpillar - Reunião (copy) (copy)</t>
@@ -765,55 +801,79 @@
     <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
   </si>
   <si>
+    <t>9703863877</t>
+  </si>
+  <si>
     <t>O cadastro de indicadores não está funcionando</t>
   </si>
   <si>
-    <t>30/07/2025</t>
+    <t>9685266241</t>
+  </si>
+  <si>
+    <t>9703874953</t>
   </si>
   <si>
     <t>Precisamos que seja possível incluir valores negativos no resultado dos indicadores, como -6,14, -3,25...</t>
   </si>
   <si>
+    <t>9703884084</t>
+  </si>
+  <si>
     <t>A média precisa ser editável, hoje ela é calculada automaticamente de acordo com os resultados inseridos, e precisamos que continue automática, porém com a possibilidade de editar, pois em alguns indicadores são feitas as médias ponderadas.</t>
   </si>
   <si>
+    <t>9689805355</t>
+  </si>
+  <si>
     <t>Agendamento industrialização - Buscar notas de retorno</t>
   </si>
   <si>
+    <t>9703897908</t>
+  </si>
+  <si>
     <t>Precisamos adicionar mais uma condição no cadastro do indicador, assim como selecionamos o calendário comercial ou normal, é preciso selecionar se o indicador é de monitoramento interno ou não, exemplo:</t>
   </si>
   <si>
+    <t>9703922393</t>
+  </si>
+  <si>
     <t>Essa mesma condição de “indicador do SGI” e “indicador de monitoramento interno” precisa aparecer como opção no dashboard inicia</t>
   </si>
   <si>
+    <t>9689804455</t>
+  </si>
+  <si>
     <t>Agendamento industrialização - Buscar notas de remessa</t>
   </si>
   <si>
+    <t>9703929455</t>
+  </si>
+  <si>
     <t>No cadastro de plano de ação, quando eu seleciono a situação, o % de conclusão deve ser preenchido automaticamente dessa forma: planejada – 25%; em andamento – 50%; finalizada – 75%; eficaz – 100%.</t>
   </si>
   <si>
-    <t>26428</t>
+    <t>9693552956</t>
   </si>
   <si>
     <t>CONSULTA EMBARQUES ALTONA</t>
   </si>
   <si>
-    <t>29/07/2025</t>
-  </si>
-  <si>
-    <t>33147</t>
+    <t>9698357710</t>
   </si>
   <si>
     <t>Restrição de sistema refugo</t>
   </si>
   <si>
-    <t>32746</t>
+    <t>9708266904</t>
   </si>
   <si>
     <t>Finalizar Fluxos 90</t>
   </si>
   <si>
-    <t>33098</t>
+    <t>02/08/2025</t>
+  </si>
+  <si>
+    <t>9776118411</t>
   </si>
   <si>
     <t>Trava alteração em FTF com produtivo</t>
@@ -825,7 +885,7 @@
     <t>Agosto</t>
   </si>
   <si>
-    <t>33333</t>
+    <t>9779448893</t>
   </si>
   <si>
     <t>Análise Base de Dados Apontamentos Acabamento USE</t>
@@ -837,7 +897,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-16</t>
+    <t>Mai/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -1564,13 +1624,13 @@
         <v>40</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>43</v>
@@ -1611,13 +1671,13 @@
         <v>40</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>43</v>
@@ -1628,7 +1688,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1640,10 +1700,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>31</v>
@@ -1655,13 +1715,13 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>26</v>
@@ -1675,7 +1735,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1687,10 +1747,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1702,19 +1762,19 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>44</v>
@@ -1722,46 +1782,46 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>44</v>
@@ -1769,46 +1829,46 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>44</v>
@@ -1816,7 +1876,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1828,10 +1888,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1843,19 +1903,19 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>44</v>
@@ -1863,7 +1923,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1875,10 +1935,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
@@ -1890,19 +1950,19 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>44</v>
@@ -1910,7 +1970,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1922,10 +1982,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1937,10 +1997,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1957,7 +2017,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1969,10 +2029,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1984,16 +2044,16 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>43</v>
@@ -2004,7 +2064,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -2016,10 +2076,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -2031,19 +2091,19 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>44</v>
@@ -2051,7 +2111,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -2063,10 +2123,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>31</v>
@@ -2078,19 +2138,19 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>44</v>
@@ -2098,7 +2158,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -2110,10 +2170,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -2125,7 +2185,7 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>24</v>
@@ -2137,7 +2197,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>44</v>
@@ -2145,7 +2205,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -2157,10 +2217,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -2172,16 +2232,16 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>43</v>
@@ -2192,7 +2252,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -2204,10 +2264,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -2219,7 +2279,7 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>24</v>
@@ -2231,7 +2291,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>44</v>
@@ -2239,7 +2299,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2251,10 +2311,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>31</v>
@@ -2266,19 +2326,19 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>44</v>
@@ -2286,7 +2346,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2298,10 +2358,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>31</v>
@@ -2313,19 +2373,19 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>44</v>
@@ -2333,7 +2393,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2345,10 +2405,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2360,19 +2420,19 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>44</v>
@@ -2380,22 +2440,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2407,19 +2467,19 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>44</v>
@@ -2427,7 +2487,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2439,10 +2499,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2457,10 +2517,10 @@
         <v>32</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>26</v>
@@ -2474,7 +2534,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2483,31 +2543,31 @@
         <v>17</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>26</v>
@@ -2521,7 +2581,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2533,10 +2593,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2548,7 +2608,7 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
@@ -2560,7 +2620,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>44</v>
@@ -2568,7 +2628,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2580,10 +2640,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2595,19 +2655,19 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>44</v>
@@ -2615,7 +2675,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2627,10 +2687,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2642,19 +2702,19 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>44</v>
@@ -2662,7 +2722,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2674,10 +2734,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2709,7 +2769,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2721,10 +2781,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2736,19 +2796,19 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>44</v>
@@ -2756,7 +2816,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2768,10 +2828,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2783,19 +2843,19 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>44</v>
@@ -2803,7 +2863,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2815,10 +2875,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2830,19 +2890,19 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>44</v>
@@ -2850,7 +2910,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2862,10 +2922,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2877,19 +2937,19 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>44</v>
@@ -2897,7 +2957,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2909,10 +2969,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2924,16 +2984,16 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>43</v>
@@ -2944,7 +3004,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2956,10 +3016,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2971,19 +3031,19 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>44</v>
@@ -2991,7 +3051,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -3003,10 +3063,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -3018,19 +3078,19 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>34</v>
@@ -3038,7 +3098,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -3050,10 +3110,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -3065,19 +3125,19 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>34</v>
@@ -3085,7 +3145,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -3097,10 +3157,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -3112,19 +3172,19 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>44</v>
@@ -3132,7 +3192,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -3144,25 +3204,25 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -3171,7 +3231,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>34</v>
@@ -3179,46 +3239,46 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>44</v>
@@ -3226,7 +3286,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -3238,10 +3298,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3253,7 +3313,7 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>24</v>
@@ -3265,7 +3325,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>44</v>
@@ -3273,22 +3333,22 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3300,19 +3360,19 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>44</v>
@@ -3320,7 +3380,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3332,10 +3392,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3347,19 +3407,19 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>44</v>
@@ -3367,46 +3427,46 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>44</v>
@@ -3414,46 +3474,46 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>44</v>
@@ -3461,7 +3521,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3473,10 +3533,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3488,19 +3548,19 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>44</v>
@@ -3508,7 +3568,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3520,10 +3580,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3535,19 +3595,19 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>44</v>
@@ -3555,7 +3615,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3567,10 +3627,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3582,7 +3642,7 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>24</v>
@@ -3594,7 +3654,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>44</v>
@@ -3602,7 +3662,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3614,10 +3674,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3629,19 +3689,19 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>44</v>
@@ -3649,7 +3709,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3661,10 +3721,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3676,7 +3736,7 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>24</v>
@@ -3688,7 +3748,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>44</v>
@@ -3696,7 +3756,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3708,10 +3768,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3723,19 +3783,19 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>44</v>
@@ -3743,22 +3803,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3770,19 +3830,19 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>44</v>
@@ -3790,7 +3850,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3802,10 +3862,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3817,19 +3877,19 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>44</v>
@@ -3837,7 +3897,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3849,10 +3909,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3864,16 +3924,16 @@
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>27</v>
@@ -3884,7 +3944,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3896,10 +3956,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3911,19 +3971,19 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>44</v>
@@ -3931,7 +3991,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3943,10 +4003,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3958,7 +4018,7 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>24</v>
@@ -3970,7 +4030,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>34</v>
@@ -3978,7 +4038,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3990,10 +4050,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -4005,19 +4065,19 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>44</v>
@@ -4025,7 +4085,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -4037,10 +4097,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -4052,19 +4112,19 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>44</v>
@@ -4072,46 +4132,46 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>44</v>
@@ -4119,7 +4179,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -4131,10 +4191,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -4149,13 +4209,13 @@
         <v>40</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>43</v>
@@ -4166,37 +4226,37 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>40</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>25</v>
@@ -4213,7 +4273,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4225,10 +4285,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4243,13 +4303,13 @@
         <v>40</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>43</v>
@@ -4260,7 +4320,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4272,10 +4332,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4287,19 +4347,19 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>44</v>
@@ -4307,7 +4367,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4319,10 +4379,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4334,19 +4394,19 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>44</v>
@@ -4354,46 +4414,46 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>44</v>
@@ -4401,7 +4461,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4413,10 +4473,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4428,19 +4488,19 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>44</v>
@@ -4448,7 +4508,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
@@ -4460,10 +4520,10 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
@@ -4475,19 +4535,19 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>44</v>
@@ -4495,46 +4555,46 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>44</v>
@@ -4542,22 +4602,22 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4569,19 +4629,19 @@
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>44</v>
@@ -4589,7 +4649,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -4601,10 +4661,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -4616,7 +4676,7 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>24</v>
@@ -4628,7 +4688,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>44</v>
@@ -4636,46 +4696,46 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>44</v>
@@ -4683,46 +4743,46 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>44</v>
@@ -4730,7 +4790,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4742,10 +4802,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4757,19 +4817,19 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>44</v>
@@ -4777,22 +4837,22 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
@@ -4804,19 +4864,19 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>44</v>
@@ -4824,46 +4884,46 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>44</v>
@@ -4871,7 +4931,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4883,10 +4943,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>31</v>
@@ -4898,19 +4958,19 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>44</v>
@@ -4918,7 +4978,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
@@ -4930,10 +4990,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>31</v>
@@ -4945,19 +5005,19 @@
         <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>44</v>
@@ -4965,46 +5025,46 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>44</v>
@@ -5012,46 +5072,46 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>44</v>
@@ -5059,22 +5119,22 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>136</v>
+        <v>227</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
@@ -5086,19 +5146,19 @@
         <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>44</v>
@@ -5106,7 +5166,7 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
@@ -5118,10 +5178,10 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -5133,19 +5193,19 @@
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>44</v>
@@ -5153,37 +5213,37 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>25</v>
@@ -5192,7 +5252,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>44</v>
@@ -5200,7 +5260,7 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
@@ -5212,10 +5272,10 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -5227,19 +5287,19 @@
         <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>24</v>
+        <v>239</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O83" s="2" t="s">
         <v>44</v>
@@ -5247,46 +5307,46 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>44</v>
@@ -5294,7 +5354,7 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
@@ -5306,10 +5366,10 @@
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5321,19 +5381,19 @@
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O85" s="2" t="s">
         <v>44</v>
@@ -5341,7 +5401,7 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
@@ -5353,10 +5413,10 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5368,19 +5428,19 @@
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O86" s="2" t="s">
         <v>44</v>
@@ -5388,7 +5448,7 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>16</v>
@@ -5400,10 +5460,10 @@
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
@@ -5415,19 +5475,19 @@
         <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O87" s="2" t="s">
         <v>44</v>
@@ -5435,7 +5495,7 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
@@ -5447,10 +5507,10 @@
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>20</v>
@@ -5462,19 +5522,19 @@
         <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O88" s="2" t="s">
         <v>44</v>
@@ -5482,22 +5542,22 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
@@ -5509,19 +5569,19 @@
         <v>22</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O89" s="2" t="s">
         <v>44</v>
@@ -5529,7 +5589,7 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>16</v>
@@ -5541,10 +5601,10 @@
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
@@ -5556,7 +5616,7 @@
         <v>22</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>24</v>
@@ -5568,7 +5628,7 @@
         <v>26</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O90" s="2" t="s">
         <v>44</v>
@@ -5576,7 +5636,7 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>16</v>
@@ -5588,10 +5648,10 @@
         <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>20</v>
@@ -5603,19 +5663,19 @@
         <v>22</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O91" s="2" t="s">
         <v>44</v>
@@ -5623,7 +5683,7 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>16</v>
@@ -5635,10 +5695,10 @@
         <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>20</v>
@@ -5650,7 +5710,7 @@
         <v>22</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>24</v>
@@ -5662,7 +5722,7 @@
         <v>26</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O92" s="2" t="s">
         <v>44</v>
@@ -5670,7 +5730,7 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>16</v>
@@ -5682,10 +5742,10 @@
         <v>18</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>20</v>
@@ -5697,7 +5757,7 @@
         <v>22</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>24</v>
@@ -5709,7 +5769,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O93" s="2" t="s">
         <v>44</v>
@@ -5717,37 +5777,37 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>25</v>
@@ -5756,7 +5816,7 @@
         <v>26</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O94" s="2" t="s">
         <v>44</v>
@@ -5764,7 +5824,7 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>16</v>
@@ -5776,10 +5836,10 @@
         <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>20</v>
@@ -5791,16 +5851,16 @@
         <v>22</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>251</v>
+        <v>96</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>27</v>
@@ -5811,7 +5871,7 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>55</v>
+        <v>264</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>16</v>
@@ -5823,10 +5883,10 @@
         <v>18</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>20</v>
@@ -5838,19 +5898,19 @@
         <v>22</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="M96" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O96" s="2" t="s">
         <v>44</v>
@@ -5858,7 +5918,7 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>158</v>
+        <v>265</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>16</v>
@@ -5870,10 +5930,10 @@
         <v>18</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>20</v>
@@ -5885,16 +5945,16 @@
         <v>22</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>251</v>
+        <v>96</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>27</v>
@@ -5905,7 +5965,7 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>158</v>
+        <v>267</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>16</v>
@@ -5917,10 +5977,10 @@
         <v>18</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>20</v>
@@ -5932,16 +5992,16 @@
         <v>22</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>251</v>
+        <v>96</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>27</v>
@@ -5952,22 +6012,22 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>136</v>
+        <v>269</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>20</v>
@@ -5979,19 +6039,19 @@
         <v>22</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O99" s="2" t="s">
         <v>44</v>
@@ -5999,7 +6059,7 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>158</v>
+        <v>271</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>16</v>
@@ -6011,10 +6071,10 @@
         <v>18</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>20</v>
@@ -6026,16 +6086,16 @@
         <v>22</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>251</v>
+        <v>96</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N100" s="2" t="s">
         <v>27</v>
@@ -6046,7 +6106,7 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>158</v>
+        <v>273</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>16</v>
@@ -6058,10 +6118,10 @@
         <v>18</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>20</v>
@@ -6073,16 +6133,16 @@
         <v>22</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>251</v>
+        <v>96</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>27</v>
@@ -6093,22 +6153,22 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>136</v>
+        <v>275</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>20</v>
@@ -6120,19 +6180,19 @@
         <v>22</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O102" s="2" t="s">
         <v>44</v>
@@ -6140,7 +6200,7 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>158</v>
+        <v>277</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>16</v>
@@ -6152,10 +6212,10 @@
         <v>18</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>20</v>
@@ -6167,16 +6227,16 @@
         <v>22</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>251</v>
+        <v>96</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N103" s="2" t="s">
         <v>27</v>
@@ -6187,7 +6247,7 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>16</v>
@@ -6199,10 +6259,10 @@
         <v>18</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>20</v>
@@ -6214,16 +6274,16 @@
         <v>22</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>261</v>
+        <v>90</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N104" s="2" t="s">
         <v>27</v>
@@ -6234,7 +6294,7 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>16</v>
@@ -6246,10 +6306,10 @@
         <v>18</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>20</v>
@@ -6261,16 +6321,16 @@
         <v>22</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>261</v>
+        <v>90</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N105" s="2" t="s">
         <v>27</v>
@@ -6281,7 +6341,7 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>16</v>
@@ -6293,10 +6353,10 @@
         <v>18</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>20</v>
@@ -6308,16 +6368,16 @@
         <v>22</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>251</v>
+        <v>96</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>24</v>
+        <v>285</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N106" s="2" t="s">
         <v>27</v>
@@ -6328,7 +6388,7 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>16</v>
@@ -6340,10 +6400,10 @@
         <v>18</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>20</v>
@@ -6355,27 +6415,27 @@
         <v>22</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>16</v>
@@ -6387,10 +6447,10 @@
         <v>18</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>20</v>
@@ -6402,22 +6462,22 @@
         <v>22</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N108" s="2" t="s">
         <v>43</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -6433,23 +6493,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="B2" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="D2" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="E2" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6457,16 +6517,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6477,20 +6537,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>303</v>
+        <v>22.17</v>
       </c>
       <c r="J5" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K22">
         <v>67</v>
@@ -6498,7 +6558,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K23">
         <v>3</v>
@@ -6506,7 +6566,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6537,12 +6597,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="B2">
         <v>107</v>
@@ -6556,35 +6616,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>303</v>
+        <v>22.17</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6592,7 +6652,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -6601,19 +6661,19 @@
         <v>81</v>
       </c>
       <c r="G10" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N10">
         <v>67</v>
@@ -6622,15 +6682,15 @@
         <v>33</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
         <v>36</v>
@@ -6645,10 +6705,10 @@
         <v>20</v>
       </c>
       <c r="J11" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="K11">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="M11" t="s">
         <v>25</v>
@@ -6660,18 +6720,18 @@
         <v>43</v>
       </c>
       <c r="Q11">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E12">
         <v>5</v>
@@ -6683,59 +6743,71 @@
         <v>87</v>
       </c>
       <c r="J12" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="K12">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E13">
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N13">
         <v>14</v>
       </c>
       <c r="P13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Q13">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
       <c r="G14" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="N14">
         <v>3</v>
@@ -6744,12 +6816,12 @@
         <v>27</v>
       </c>
       <c r="Q14">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N15">
         <v>2</v>
@@ -6757,7 +6829,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6765,7 +6837,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6773,10 +6845,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -6784,7 +6856,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6792,142 +6864,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>295</v>
+        <v>369</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>281</v>
+        <v>369</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
